--- a/dcf/WPM.xlsx
+++ b/dcf/WPM.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>64.89381299516891</v>
+        <v>58.4096824558651</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>62.54903524624759</v>
+        <v>56.33541721912702</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>60.31162202449326</v>
+        <v>54.35585573644873</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>58.17610588376377</v>
+        <v>52.46618173536742</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>56.13732306799236</v>
+        <v>50.66184627105142</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>54.19039531132542</v>
+        <v>48.93855171251616</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>52.33071280625792</v>
+        <v>47.29223675625839</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>69.33954363016106</v>
+        <v>62.31693779933961</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>66.79816842700998</v>
+        <v>60.06988736335742</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>64.37367875443999</v>
+        <v>57.92590848293255</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>62.06010636896588</v>
+        <v>55.87974474577916</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>59.85181512891231</v>
+        <v>53.92643203769419</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>57.74348106624475</v>
+        <v>52.06128100980212</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>55.73007373855297</v>
+        <v>50.2798606717887</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>73.78527426515321</v>
+        <v>66.22419314281412</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>71.04730160777238</v>
+        <v>63.80435750758784</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>68.43573548438674</v>
+        <v>61.49596122941638</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>65.944106854168</v>
+        <v>59.29330775619092</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>63.56630718983226</v>
+        <v>57.19101780433697</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>61.29656682116408</v>
+        <v>55.18401030708808</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>59.12943467084802</v>
+        <v>53.26748458731902</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>78.23100490014535</v>
+        <v>70.13144848628862</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>75.29643478853477</v>
+        <v>67.53882765181825</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>72.49779221433347</v>
+        <v>65.0660139759002</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>69.82810733937011</v>
+        <v>62.70687076660268</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>67.28079925075221</v>
+        <v>60.45560357097976</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>64.8496525760834</v>
+        <v>58.30673960437405</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>62.52879560314307</v>
+        <v>56.25510850284933</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>82.67673553513748</v>
+        <v>74.03870382976314</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>79.54556796929715</v>
+        <v>71.27329779604867</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>76.55984894428022</v>
+        <v>68.63606672238403</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>73.71210782457223</v>
+        <v>66.12043377701443</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>70.99529131167216</v>
+        <v>63.72018933762253</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>68.40273833100274</v>
+        <v>61.42946890166001</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>65.92815653543811</v>
+        <v>59.24273241837965</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>87.12246617012963</v>
+        <v>77.94595917323764</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>83.79470115005955</v>
+        <v>75.00776794027908</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>80.62190567422695</v>
+        <v>72.20611946886784</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>77.59610830977434</v>
+        <v>69.53399678742618</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>74.70978337259211</v>
+        <v>66.9847751042653</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>71.95582408592206</v>
+        <v>64.55219819894596</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>69.32751746773316</v>
+        <v>62.23035633390996</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>91.56819680512177</v>
+        <v>81.85321451671213</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>88.04383433082194</v>
+        <v>78.74223808450949</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>84.6839624041737</v>
+        <v>75.77617221535168</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>81.48010879497645</v>
+        <v>72.94755979783793</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>78.42427543351207</v>
+        <v>70.24936087090809</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>75.50890984084138</v>
+        <v>67.67492749623192</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>72.7268784000282</v>
+        <v>65.21798024944029</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>115.7300033569336</v>
+        <v>112.4000015258789</v>
       </c>
     </row>
     <row r="14">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.030331962926482</v>
+        <v>1.032139617933484</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>115.7300033569336</v>
+        <v>112.4000015258789</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>69.82810733937011</v>
+        <v>62.70687076660268</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>93.36075776728991</v>
+        <v>81.77863444923197</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>51.68408989622353</v>
+        <v>47.58682006413546</v>
       </c>
     </row>
     <row r="59">
